--- a/evaluation_history.xlsx
+++ b/evaluation_history.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="city" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ipl" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="General" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ipl" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="bank" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="bank" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="city" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,71 +447,76 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>local068</t>
+          <t>local020</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>local070</t>
+          <t>local021</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>local071</t>
+          <t>local022</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>local072</t>
+          <t>local023</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>local167</t>
+          <t>local024</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>local168</t>
+          <t>local025</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>local169</t>
+          <t>local026</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>local170</t>
+          <t>local228</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>local171</t>
+          <t>local229</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>local202</t>
+          <t>local258</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>local259</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 21:25:21</t>
+          <t>2026-03-26 21:26:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_city_legislation_0326</t>
+          <t>test_ipl4_0326</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
@@ -529,10 +534,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -543,26 +548,27 @@
       <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 21:30:52</t>
+          <t>2026-03-26 22:08:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test_critic_city_0326</t>
+          <t>test_ipl5_0326</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
@@ -577,46 +583,47 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 21:47:10</t>
+          <t>2026-03-27 09:14:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_city_legislation2_0326</t>
+          <t>test_ipl_0327</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>44.44</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -627,11 +634,9 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -645,29 +650,30 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27 02:23:22</t>
+          <t>2026-04-08 18:36:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test_city2_0327</t>
+          <t>test_flash_ipl_0408</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>45.45</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -685,119 +691,22 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-27 09:29:02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>test_city_legi_0327</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>77.78</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-04-07 16:35:51</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>llmtest_2.5pro_city_0407</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>90</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,6 +1392,152 @@
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:05:18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hard6_0408</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-09 08:57:37</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test_city_0409</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1494,7 +1549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,82 +1580,102 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>local020</t>
+          <t>local064</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>local021</t>
+          <t>local074</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>local022</t>
+          <t>local075</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>local023</t>
+          <t>local077</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>local024</t>
+          <t>local078</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>local025</t>
+          <t>local156</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>local026</t>
+          <t>local157</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>local228</t>
+          <t>local284</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>local229</t>
+          <t>local285</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>local258</t>
+          <t>local297</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>local259</t>
+          <t>local298</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>local299</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>local300</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>local301</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>local302</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 21:26:21</t>
+          <t>2026-03-26 21:24:23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_ipl4_0326</t>
+          <t>test_bank_sales3_0326</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>54.55</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1609,50 +1684,56 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 22:08:48</t>
+          <t>2026-03-26 21:25:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test_ipl5_0326</t>
+          <t>test_bank_sales2_0326</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>42.86</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1668,43 +1749,55 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27 09:14:30</t>
+          <t>2026-03-26 21:25:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_ipl_0327</t>
+          <t>test_bank_sales_0326</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44.44</v>
+        <v>66.67</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1712,49 +1805,59 @@
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08 18:36:00</t>
+          <t>2026-03-26 21:27:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test_flash_ipl_0408</t>
+          <t>test_bank2_0325</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.45</v>
+        <v>63.64</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1768,23 +1871,1065 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:27:57</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test_bank4_0325</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:28:03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test_bank5_0325</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:28:09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test_bank6_0325</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:28:15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test_bank7_0325</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:28:20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>test_bank8_0325</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-26 21:28:25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>test_bank9_0325</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-07 15:28:12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>llmtest_2.5pro_bank_0407</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:12:27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>llmtest_2.5pro_bank2_0407</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:00:29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>llmtest_2.5_pro_bank_0408</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-08 13:28:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>test_bank_hard_0408</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-08 14:16:18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>llmtest_bank_hard_0408</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-08 15:02:58</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hard_0408</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-08 15:43:10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hard2_0408</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-08 19:13:54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hard3_0408</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-08 20:04:03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hmm_0408</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-08 20:27:24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hard4_0408</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-08 23:11:33</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>test_flash_bank_hard6_0408</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-09 09:30:31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>test_bank_0409</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +2943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,102 +2974,77 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>local064</t>
+          <t>local068</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>local074</t>
+          <t>local070</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>local075</t>
+          <t>local071</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>local077</t>
+          <t>local072</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>local078</t>
+          <t>local167</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>local156</t>
+          <t>local168</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>local157</t>
+          <t>local169</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>local284</t>
+          <t>local170</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>local285</t>
+          <t>local171</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>local297</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>local298</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>local299</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>local300</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>local301</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>local302</t>
+          <t>local202</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 21:24:23</t>
+          <t>2026-03-26 21:25:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_bank_sales3_0326</t>
+          <t>test_city_legislation_0326</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>54.55</v>
+        <v>80</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1933,56 +3053,49 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26 21:25:00</t>
+          <t>2026-03-26 21:30:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test_bank_sales2_0326</t>
+          <t>test_critic_city_0326</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.86</v>
+        <v>80</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1991,62 +3104,49 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26 21:25:07</t>
+          <t>2026-03-26 21:47:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_bank_sales_0326</t>
+          <t>test_city_legislation2_0326</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -2060,53 +3160,44 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26 21:27:33</t>
+          <t>2026-03-27 02:23:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test_bank2_0325</t>
+          <t>test_city2_0327</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>63.64</v>
+        <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -2120,52 +3211,43 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26 21:27:57</t>
+          <t>2026-03-27 09:29:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>test_bank4_0325</t>
+          <t>test_city_legi_0327</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>1</v>
       </c>
@@ -2179,59 +3261,46 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-26 21:28:03</t>
+          <t>2026-04-07 16:35:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>test_bank5_0325</t>
+          <t>llmtest_2.5pro_city_0407</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>46.15</v>
+        <v>90</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -2242,55 +3311,44 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26 21:28:09</t>
+          <t>2026-04-08 19:39:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>test_bank6_0325</t>
+          <t>test_flash_city_hmm_0408</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.14</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -2304,7 +3362,9 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
@@ -2315,113 +3375,69 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26 21:28:15</t>
+          <t>2026-04-08 23:49:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>test_bank7_0325</t>
+          <t>test_tset_</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26 21:28:20</t>
+          <t>2026-04-09 00:03:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>test_bank8_0325</t>
+          <t>test_flash_city_0408_final</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>53.33</v>
+        <v>70</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -2445,114 +3461,72 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26 21:28:25</t>
+          <t>2026-04-09 10:01:38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>test_bank9_0325</t>
+          <t>test_0409</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.86</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07 15:28:12</t>
+          <t>2026-04-09 10:12:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>llmtest_2.5pro_bank_0407</t>
+          <t>test_city2_0409</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72.73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2560,7 +3534,9 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
@@ -2571,48 +3547,37 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-07 18:12:27</t>
+          <t>2026-04-09 10:25:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>llmtest_2.5pro_bank2_0407</t>
+          <t>test_city3_0409</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69.23</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2620,7 +3585,9 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
@@ -2631,327 +3598,82 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-08 13:00:29</t>
+          <t>2026-04-09 10:36:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>llmtest_2.5_pro_bank_0408</t>
+          <t>test_city_hard_0409</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.56</v>
+        <v>33.33</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08 13:28:23</t>
+          <t>2026-04-09 10:42:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>test_bank_hard_0408</t>
+          <t>test_city_hard2_0409</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-04-08 14:16:18</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>llmtest_bank_hard_0408</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-04-08 15:02:58</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>test_flash_bank_hard_0408</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-04-08 15:43:10</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>test_flash_bank_hard2_0408</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-04-08 19:13:54</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>test_flash_bank_hard3_0408</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
